--- a/Datas/Hero.xlsx
+++ b/Datas/Hero.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,12 @@
     <t>SkillIds</t>
   </si>
   <si>
+    <t>BulletId</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -64,16 +70,13 @@
     <t>list,int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
-    <t>剑士</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>法师</t>
+    <t>爱丽丝</t>
   </si>
 </sst>
 </file>
@@ -1007,10 +1010,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1032,41 +1035,53 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9">
       <c r="B4">
         <v>2001</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -1080,46 +1095,15 @@
       <c r="G4" s="1">
         <v>101102</v>
       </c>
+      <c r="H4">
+        <v>20001</v>
+      </c>
+      <c r="I4">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="B5">
-        <v>2002</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>200</v>
-      </c>
-      <c r="E5">
-        <v>50</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6">
-        <v>2003</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>200</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
-      <c r="G6" s="1">
-        <v>104105</v>
-      </c>
+    <row r="6" spans="1:9">
+      <c r="G6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/Hero.xlsx
+++ b/Datas/Hero.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -58,6 +58,9 @@
     <t>AttackSpeed</t>
   </si>
   <si>
+    <t>PrefabName</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
   </si>
   <si>
     <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>alice</t>
   </si>
 </sst>
 </file>
@@ -1010,10 +1016,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1041,47 +1047,53 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="B4">
         <v>2001</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -1096,13 +1108,16 @@
         <v>101102</v>
       </c>
       <c r="H4">
-        <v>20001</v>
+        <v>20002</v>
       </c>
       <c r="I4">
         <v>0.5</v>
       </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="G6" s="1"/>
     </row>
   </sheetData>
